--- a/data/assainissement.xlsx
+++ b/data/assainissement.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="convention" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
   <si>
     <t xml:space="preserve">cle</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t xml:space="preserve">responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">progression</t>
   </si>
   <si>
     <t xml:space="preserve">STEP Choisy / Avrigny</t>
@@ -785,7 +788,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,25 +810,31 @@
       <c r="F1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -833,19 +842,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>33</v>
+      <c r="G3" s="1" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -853,19 +865,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -873,19 +885,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="n">
         <v>42</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -893,19 +908,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +944,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
@@ -937,42 +952,42 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -996,22 +1011,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">SUMIF(A:A,"poste",C:C)</f>
@@ -1024,10 +1039,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>80000</v>
@@ -1039,10 +1054,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>20000</v>
@@ -1054,10 +1069,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>28000</v>
@@ -1069,10 +1084,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>22000</v>
@@ -1103,10 +1118,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
